--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512400_1ºE1ºOFINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512400_1ºE1ºOFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6499</v>
+        <v>7.0171</v>
       </c>
       <c r="E2" t="n">
-        <v>5.269</v>
+        <v>4.6204</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3809</v>
+        <v>2.3967</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3016</v>
+        <v>4.3228</v>
       </c>
       <c r="H2" t="n">
-        <v>3.22</v>
+        <v>3.2596</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0816</v>
+        <v>1.0632</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5957</v>
+        <v>4.6635</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2796</v>
+        <v>4.3454</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3161</v>
+        <v>0.318</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2941</v>
+        <v>-0.3407</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0596</v>
+        <v>-1.0859</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7655</v>
+        <v>0.7452</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6853</v>
+        <v>1.0624</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3698</v>
+        <v>0.6452</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3155</v>
+        <v>0.4172</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.387</v>
+        <v>6.4177</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9739</v>
+        <v>6.7864</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5869</v>
+        <v>-0.3688</v>
       </c>
       <c r="G3" t="n">
-        <v>6.307</v>
+        <v>6.3392</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0268</v>
+        <v>2.0544</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2802</v>
+        <v>4.2848</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6289</v>
+        <v>6.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8355</v>
+        <v>2.8836</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7934</v>
+        <v>3.8165</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3219</v>
+        <v>-0.3608</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8087</v>
+        <v>-0.8292</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4868</v>
+        <v>0.4684</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8569</v>
+        <v>0.1994</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.655</v>
+        <v>0.0864</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2019</v>
+        <v>0.113</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.9068</v>
+        <v>-1.943</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9068</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2728</v>
+        <v>5.0044</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7956</v>
+        <v>2.2682</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5228</v>
+        <v>2.7362</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6574</v>
+        <v>3.5343</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6951</v>
+        <v>1.797</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0377</v>
+        <v>1.7373</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3973</v>
+        <v>3.4799</v>
       </c>
       <c r="K4" t="n">
-        <v>1.528</v>
+        <v>2.4878</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8693</v>
+        <v>0.9921</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7399</v>
+        <v>0.0544</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1671</v>
+        <v>-0.6908</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.907</v>
+        <v>0.7452</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2291</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2291</v>
+        <v>2.0245</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1443</v>
+        <v>1.2922</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1563</v>
+        <v>0.6349</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.012</v>
+        <v>0.6573</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2421</v>
+        <v>1.1902</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2421</v>
+        <v>1.1902</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7364</v>
+        <v>3.389</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5885</v>
+        <v>3.8534</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1479</v>
+        <v>-0.4644</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4695</v>
+        <v>0.6585</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7621</v>
+        <v>1.7186</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7074</v>
+        <v>-1.06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3734</v>
+        <v>2.4346</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4314</v>
+        <v>1.56</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9419</v>
+        <v>0.8746</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09619999999999999</v>
+        <v>-1.7761</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6693</v>
+        <v>0.1586</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7655</v>
+        <v>-1.9346</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0242</v>
+        <v>1.2147</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0727</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0485</v>
+        <v>1.2147</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1105</v>
+        <v>1.2648</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1073</v>
+        <v>1.1678</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0032</v>
+        <v>0.097</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1806</v>
+        <v>0.2509</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1806</v>
+        <v>0.2509</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4031</v>
+        <v>2.6535</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7271</v>
+        <v>3.2092</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3239</v>
+        <v>-0.5557</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6335</v>
+        <v>3.629</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4431</v>
+        <v>0.4353</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1904</v>
+        <v>3.1938</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2341</v>
+        <v>5.2667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1366</v>
+        <v>0.1383</v>
       </c>
       <c r="L6" t="n">
-        <v>5.0974</v>
+        <v>5.1284</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6006</v>
+        <v>-1.6376</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3065</v>
+        <v>0.297</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.907</v>
+        <v>-1.9346</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1317</v>
+        <v>0.1337</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4585</v>
+        <v>-0.033</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3268</v>
+        <v>0.1667</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2707</v>
+        <v>1.8312</v>
       </c>
       <c r="E7" t="n">
-        <v>2.923</v>
+        <v>2.7067</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6524</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.065</v>
+        <v>0.0837</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4408</v>
+        <v>-1.4241</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5058</v>
+        <v>1.5078</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2659</v>
+        <v>1.3402</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6599</v>
+        <v>-0.6151</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9258</v>
+        <v>1.9552</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2009</v>
+        <v>-1.2565</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7809</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.42</v>
+        <v>-0.4474</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1944</v>
+        <v>1.7714</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5008</v>
+        <v>1.1885</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6936</v>
+        <v>0.5829</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6966</v>
+        <v>1.7334</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2325</v>
+        <v>2.4069</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5359</v>
+        <v>-0.6735</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0117</v>
+        <v>2.0368</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9593</v>
+        <v>0.987</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0524</v>
+        <v>1.0499</v>
       </c>
       <c r="J8" t="n">
-        <v>2.822</v>
+        <v>2.8794</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7922</v>
+        <v>0.8284</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0298</v>
+        <v>2.051</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8103</v>
+        <v>-0.8425</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1671</v>
+        <v>0.1586</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9774</v>
+        <v>-1.0011</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5312</v>
+        <v>-0.4819</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5895</v>
+        <v>-0.4725</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0583</v>
+        <v>-0.0094</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0623</v>
+        <v>1.7157</v>
       </c>
       <c r="E9" t="n">
-        <v>2.64</v>
+        <v>3.1482</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5777</v>
+        <v>-1.4325</v>
       </c>
       <c r="G9" t="n">
-        <v>5.5751</v>
+        <v>5.6209</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2003</v>
+        <v>-0.179</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7755</v>
+        <v>5.7999</v>
       </c>
       <c r="J9" t="n">
-        <v>7.5383</v>
+        <v>7.6335</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1345</v>
+        <v>0.1758</v>
       </c>
       <c r="L9" t="n">
-        <v>7.4038</v>
+        <v>7.4577</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9631</v>
+        <v>-2.0126</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3348</v>
+        <v>-0.3548</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6283</v>
+        <v>-1.6578</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.5067</v>
+        <v>-4.4539</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.1455</v>
+        <v>-6.0735</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1001</v>
+        <v>0.642</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1728</v>
+        <v>0.4913</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0727</v>
+        <v>0.1507</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1062</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0744</v>
+        <v>1.097</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0701</v>
+        <v>0.4883</v>
       </c>
       <c r="E10" t="n">
-        <v>1.66</v>
+        <v>-1.6811</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5899</v>
+        <v>2.1694</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2527</v>
+        <v>-0.95</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0302</v>
+        <v>-1.3432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2829</v>
+        <v>0.3932</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2252</v>
+        <v>-0.2295</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1973</v>
+        <v>-0.3958</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4225</v>
+        <v>0.1663</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9725</v>
+        <v>-0.7205</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1671</v>
+        <v>-0.9474</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1396</v>
+        <v>0.2269</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6145</v>
+        <v>1.2147</v>
       </c>
       <c r="Q10" t="n">
+        <v>-1.0123</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.227</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.6629</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.4374</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.4374</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.6145</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3835</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.4348</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.0513</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-1.1806</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.1806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.2304</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5866</v>
+        <v>1.8109</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5098</v>
+        <v>-1.5806</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9228</v>
+        <v>0.2725</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3243</v>
+        <v>-0.0015</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4014</v>
+        <v>0.2739</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2565</v>
+        <v>1.2711</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.404</v>
+        <v>-0.16</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1476</v>
+        <v>1.4312</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6664</v>
+        <v>-0.9987</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9203</v>
+        <v>0.1586</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2539</v>
+        <v>-1.1572</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2291</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2533</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.5407</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8515</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9228</v>
+        <v>0.001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4544</v>
+        <v>-1.1902</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.4544</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>30.4721</v>
+        <v>30.4807</v>
       </c>
       <c r="E12" t="n">
-        <v>28.223</v>
+        <v>29.1292</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2491</v>
+        <v>1.3513</v>
       </c>
       <c r="G12" t="n">
-        <v>25.3507</v>
+        <v>25.5477</v>
       </c>
       <c r="H12" t="n">
-        <v>7.1108</v>
+        <v>7.3041</v>
       </c>
       <c r="I12" t="n">
-        <v>18.2399</v>
+        <v>18.2438</v>
       </c>
       <c r="J12" t="n">
-        <v>34.82429999999999</v>
+        <v>35.4394</v>
       </c>
       <c r="K12" t="n">
-        <v>10.8766</v>
+        <v>11.2484</v>
       </c>
       <c r="L12" t="n">
-        <v>23.9476</v>
+        <v>24.191</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.4735</v>
+        <v>-9.891599999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.7658</v>
+        <v>-3.9443</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.707600000000001</v>
+        <v>-5.947000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>4.0969</v>
+        <v>4.0491</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.3151</v>
+        <v>-13.1594</v>
       </c>
       <c r="R12" t="n">
-        <v>17.412</v>
+        <v>17.2085</v>
       </c>
       <c r="S12" t="n">
-        <v>7.169699999999999</v>
+        <v>7.0857</v>
       </c>
       <c r="T12" t="n">
-        <v>4.1873</v>
+        <v>4.2465</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9823</v>
+        <v>2.8393</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.1451</v>
+        <v>-6.2019</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5268</v>
+        <v>2.6026</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.671900000000001</v>
+        <v>-8.804500000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0964</v>
+        <v>0.293</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7982</v>
+        <v>1.9153</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8945</v>
+        <v>-1.6223</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.2718</v>
+        <v>-4.3068</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7529</v>
+        <v>-0.77</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.5189</v>
+        <v>-3.5367</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9097</v>
+        <v>-0.8699</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1677</v>
+        <v>0.1962</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0774</v>
+        <v>-1.0661</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.3621</v>
+        <v>-3.4369</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9205</v>
+        <v>-0.9663</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.4415</v>
+        <v>-2.4706</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6941</v>
+        <v>-1.2947</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4167</v>
+        <v>-0.3965</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2774</v>
+        <v>-0.8983</v>
       </c>
       <c r="V13" t="n">
-        <v>4.0259</v>
+        <v>4.0725</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3294</v>
+        <v>3.3841</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.4674</v>
+        <v>-2.3316</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8478</v>
+        <v>2.0565</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.3152</v>
+        <v>-4.3881</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5167</v>
+        <v>-2.5444</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2872</v>
+        <v>-0.2961</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.2295</v>
+        <v>-2.2483</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0025</v>
+        <v>1.0273</v>
       </c>
       <c r="K14" t="n">
-        <v>0.884</v>
+        <v>0.9081</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.5192</v>
+        <v>-3.5717</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1712</v>
+        <v>-1.2041</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.348</v>
+        <v>-2.3676</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6395999999999999</v>
+        <v>-0.1921</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.0414</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2299</v>
+        <v>-0.2335</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.3965</v>
+        <v>-2.4414</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6491</v>
+        <v>-0.1648</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7474</v>
+        <v>-2.2766</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.3136</v>
+        <v>-2.3303</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5998</v>
+        <v>-0.631</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7138</v>
+        <v>-1.6993</v>
       </c>
       <c r="J15" t="n">
-        <v>1.104</v>
+        <v>1.1469</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0988</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0064</v>
+        <v>1.0481</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.4176</v>
+        <v>-3.4772</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6973</v>
+        <v>-0.7297</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.7203</v>
+        <v>-2.7474</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S15" t="n">
-        <v>0.122</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.524</v>
+        <v>-0.097</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6459</v>
+        <v>0.1883</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.456</v>
+        <v>-3.1615</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8476</v>
+        <v>1.3473</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.3036</v>
+        <v>-4.5088</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3618</v>
+        <v>-1.3594</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5845</v>
+        <v>-2.6269</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2227</v>
+        <v>1.2675</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5941</v>
+        <v>3.6805</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.326</v>
+        <v>-0.3167</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9201</v>
+        <v>3.9972</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.9559</v>
+        <v>-5.0399</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2586</v>
+        <v>-2.3101</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.6973</v>
+        <v>-2.7297</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.8679</v>
+        <v>-2.8343</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2393</v>
+        <v>-1.004</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.048</v>
+        <v>-0.7131</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1913</v>
+        <v>-0.2909</v>
       </c>
       <c r="V16" t="n">
-        <v>2.013</v>
+        <v>2.0362</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.2814</v>
+        <v>-3.6867</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3577</v>
+        <v>-0.835</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9237</v>
+        <v>-2.8517</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.3793</v>
+        <v>-2.7018</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1826</v>
+        <v>1.1663</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.1967</v>
+        <v>-3.8681</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8272</v>
+        <v>-0.1203</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.095</v>
+        <v>1.9162</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7322</v>
+        <v>-2.0365</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.5521</v>
+        <v>-2.5815</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0876</v>
+        <v>-0.7499</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.4645</v>
+        <v>-1.8316</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2533</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0485</v>
+        <v>1.0123</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1222</v>
+        <v>-0.1389</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2388</v>
+        <v>0.0466</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1166</v>
+        <v>-0.1855</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1806</v>
+        <v>-0.846</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4841</v>
+        <v>0.2509</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6965</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.3285</v>
+        <v>-4.3982</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5295</v>
+        <v>-0.5967</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.799</v>
+        <v>-3.8015</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6964</v>
+        <v>-3.8916</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1679</v>
+        <v>-0.6906</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.8643</v>
+        <v>-3.201</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1578</v>
+        <v>1.094</v>
       </c>
       <c r="K18" t="n">
-        <v>1.893</v>
+        <v>0.3549</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0508</v>
+        <v>0.7391</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5386</v>
+        <v>-4.9856</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7251</v>
+        <v>-1.0455</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8135</v>
+        <v>-3.9401</v>
       </c>
       <c r="P18" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.4172</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.8221</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.6606</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.2736</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.387</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.2509</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.0242</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.0242</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.7997</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-0.5895</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.2103</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.8324</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.2421</v>
-      </c>
       <c r="X18" t="n">
-        <v>-1.0744</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.5256</v>
+        <v>-4.6204</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2197</v>
+        <v>-0.3337</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.3059</v>
+        <v>-4.2867</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2123</v>
+        <v>-3.2583</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1509</v>
+        <v>-0.1766</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.0614</v>
+        <v>-3.0817</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2698</v>
+        <v>1.3072</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2157</v>
+        <v>1.2439</v>
       </c>
       <c r="L19" t="n">
-        <v>0.054</v>
+        <v>0.0633</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.482</v>
+        <v>-4.5655</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3666</v>
+        <v>-1.4205</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.1154</v>
+        <v>-3.145</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2648</v>
+        <v>-1.3376</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4167</v>
+        <v>-0.6041</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8481</v>
+        <v>-0.7335</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8264</v>
+        <v>-4.9309</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2876</v>
+        <v>-1.3473</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5388</v>
+        <v>-3.5836</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8465</v>
+        <v>0.2278</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6666</v>
+        <v>-1.0856</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.1799</v>
+        <v>1.3134</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0633</v>
+        <v>4.3957</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3375</v>
+        <v>0.6117</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7258</v>
+        <v>3.784</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.9098</v>
+        <v>-4.1679</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0041</v>
+        <v>-1.6973</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.9057</v>
+        <v>-2.4706</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4097</v>
+        <v>-2.227</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.4339</v>
+        <v>-4.4539</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8436</v>
+        <v>2.227</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1476</v>
+        <v>-1.7415</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.917</v>
+        <v>-0.9449</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2306</v>
+        <v>-0.7966</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2421</v>
+        <v>-1.1902</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3442</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2421</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0942</v>
+        <v>-5.203</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6992</v>
+        <v>-3.393</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.395</v>
+        <v>-1.8099</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2478</v>
+        <v>-5.383</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0541</v>
+        <v>-2.1936</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3019</v>
+        <v>-3.1894</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3347</v>
+        <v>-1.7699</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5911999999999999</v>
+        <v>-1.0688</v>
       </c>
       <c r="L21" t="n">
-        <v>3.7434</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.0869</v>
+        <v>-3.6131</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6453</v>
+        <v>-1.1248</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4415</v>
+        <v>-2.4883</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2533</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5067</v>
+        <v>-2.227</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2533</v>
+        <v>2.0245</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.908</v>
+        <v>-0.8077</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.179</v>
+        <v>0.1019</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.729</v>
+        <v>-0.9096</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3482</v>
+        <v>0.5019</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8324</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-30.4724</v>
+        <v>-30.4807</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2492</v>
+        <v>-1.3514</v>
       </c>
       <c r="F22" t="n">
-        <v>-28.2231</v>
+        <v>-29.1292</v>
       </c>
       <c r="G22" t="n">
-        <v>-25.3506</v>
+        <v>-25.5478</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.1107</v>
+        <v>-7.3041</v>
       </c>
       <c r="I22" t="n">
-        <v>-18.2399</v>
+        <v>-18.2436</v>
       </c>
       <c r="J22" t="n">
-        <v>9.473700000000001</v>
+        <v>9.891500000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7657</v>
+        <v>3.9443</v>
       </c>
       <c r="L22" t="n">
-        <v>5.707799999999999</v>
+        <v>5.947299999999998</v>
       </c>
       <c r="M22" t="n">
-        <v>-34.8242</v>
+        <v>-35.4393</v>
       </c>
       <c r="N22" t="n">
-        <v>-10.8763</v>
+        <v>-11.2482</v>
       </c>
       <c r="O22" t="n">
-        <v>-23.9477</v>
+        <v>-24.1909</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.096900000000001</v>
+        <v>-4.0491</v>
       </c>
       <c r="Q22" t="n">
-        <v>-17.4119</v>
+        <v>-17.2086</v>
       </c>
       <c r="R22" t="n">
-        <v>13.3149</v>
+        <v>13.1596</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.169700000000001</v>
+        <v>-7.0858</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.982600000000001</v>
+        <v>-2.8393</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.1873</v>
+        <v>-4.2466</v>
       </c>
       <c r="V22" t="n">
-        <v>6.145</v>
+        <v>6.202</v>
       </c>
       <c r="W22" t="n">
-        <v>8.671899999999999</v>
+        <v>8.804400000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.526800000000001</v>
+        <v>-2.6026</v>
       </c>
     </row>
   </sheetData>
